--- a/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
+++ b/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oversigt" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sporbarhedsmatrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analyse-moduler" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kategorier" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Oversigt" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sporbarhedsmatrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Analyse-moduler" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Kategorier" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oversigt'!$A$1:$B$1</definedName>
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.0</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +545,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>98 / 103</t>
+          <t>99 / 103</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>82, 83, 85, 90, 99</t>
+          <t>83, 85, 90, 99</t>
         </is>
       </c>
     </row>
@@ -6029,49 +6029,57 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>Periode-/rubrikafstemning mod momsangivelse</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Indgående/Udgående Moms Afstemning</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>dynamisk</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>economic</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Momskerne</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>TIL</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Opgørelse og afstemning af ind-/udgående moms; (delvis) fradragsret (momsloven)</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>analytics/categories/cat10_vat_reconciliation.py</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
           <t>test_82_period_declaration</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Indgående/Udgående Moms Afstemning</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>inaktiv_kraever_kildedata</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Momskerne</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>TIL</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>Opgørelse og afstemning af ind-/udgående moms; (delvis) fradragsret (momsloven)</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>analytics/categories/cat10_vat_reconciliation.py</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>test_82_period_declaration</t>
-        </is>
-      </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>(udfyldes — Fase C)</t>
+          <t>tests/test_validation_suite.py + validation/scenarios.py</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -7913,10 +7921,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">

--- a/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
+++ b/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1.2.0</t>
+          <t>1.3.0</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Ugyldig momssats</t>
+          <t>Sats afviger fra vat_setup</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Indtægt uden momsbehandling</t>
+          <t>Indtægt uden momsbehandling (pr. konto)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>dynamisk</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">

--- a/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
+++ b/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>

--- a/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
+++ b/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.4.0</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0 / 103</t>
+          <t>0 / 108</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>99 / 103</t>
+          <t>104 / 108</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7457,6 +7457,336 @@
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>VATA-104</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Udenlandsk valuta med indenlandsk standardmoms</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Momskerne</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>TIL</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller: valuta/kode, EU-/3.-landskøb uden RC-beregning, import, bilagstype (momsloven, Skattestyrelsens kontrolmetoder)</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>analytics/categories/cat13_cross_dimension.py</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>test_104_foreign_currency_domestic_vat</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_validation_suite.py + validation/scenarios.py</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>VATA-105</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Nulkode på udenlandsk køb</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>high, medium</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>compliance, interest_risk</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Momskerne</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>TIL</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller: valuta/kode, EU-/3.-landskøb uden RC-beregning, import, bilagstype (momsloven, Skattestyrelsens kontrolmetoder)</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>analytics/categories/cat13_cross_dimension.py</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>test_105_cross_border_purchase_no_rc</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_validation_suite.py + validation/scenarios.py</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>VATA-106</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Varekøb fra 3.-land — bekræft importørregistrering</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Momskerne</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>TIL</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller: valuta/kode, EU-/3.-landskøb uden RC-beregning, import, bilagstype (momsloven, Skattestyrelsens kontrolmetoder)</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>analytics/categories/cat13_cross_dimension.py</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>test_106_import_indicator</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_validation_suite.py + validation/scenarios.py</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>VATA-107</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Atypisk moms på bilagstype</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Momskerne</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>TIL</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller: valuta/kode, EU-/3.-landskøb uden RC-beregning, import, bilagstype (momsloven, Skattestyrelsens kontrolmetoder)</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>analytics/categories/cat13_cross_dimension.py</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>test_107_atypical_vat_by_source_code</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_validation_suite.py + validation/scenarios.py</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>VATA-108</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Salg/køb spredt over mange bilagstyper</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Momskerne</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>TIL</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller: valuta/kode, EU-/3.-landskøb uden RC-beregning, import, bilagstype (momsloven, Skattestyrelsens kontrolmetoder)</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>analytics/categories/cat13_cross_dimension.py</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>test_108_source_code_spread</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_validation_suite.py + validation/scenarios.py</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
@@ -7524,7 +7854,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7644,7 +7974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7975,6 +8305,30 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>104-108</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
+++ b/docs/VAT-Analytics_Regel-sporbarhedsmatrix.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.5.0</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -533,7 +533,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0 / 108</t>
+          <t>0 / 109</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>104 / 108</t>
+          <t>105 / 109</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7787,6 +7787,72 @@
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>VATA-109</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Fradragsprocent-afvigelse</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>dynamisk</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>economic</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Momskerne</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>TIL</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Krydsdimensionelle kontroller: valuta/kode, EU-/3.-landskøb uden RC-beregning, import, bilagstype (momsloven, Skattestyrelsens kontrolmetoder)</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>analytics/categories/cat13_cross_dimension.py</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>test_109_deduction_rate_deviation</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_validation_suite.py + validation/scenarios.py</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
@@ -7854,7 +7920,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -8316,14 +8382,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>104-108</t>
+          <t>104-109</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
